--- a/artfynd/A 30651-2024 artfynd.xlsx
+++ b/artfynd/A 30651-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1416,6 +1416,240 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118887003</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100017</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>585527</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6577547</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118887077</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105495</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Piltorp (Piltorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>585542</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6577578</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30651-2024 artfynd.xlsx
+++ b/artfynd/A 30651-2024 artfynd.xlsx
@@ -1421,7 +1421,7 @@
         <v>118887003</v>
       </c>
       <c r="B8" t="n">
-        <v>100017</v>
+        <v>100024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>118887077</v>
       </c>
       <c r="B9" t="n">
-        <v>105495</v>
+        <v>105502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 30651-2024 artfynd.xlsx
+++ b/artfynd/A 30651-2024 artfynd.xlsx
@@ -1418,10 +1418,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118887003</v>
+        <v>118887077</v>
       </c>
       <c r="B8" t="n">
-        <v>100024</v>
+        <v>105502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,20 +1430,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1454,14 +1454,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skogstorp (Skogstorp), Srm</t>
+          <t>Piltorp (Piltorp), Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585527</v>
+        <v>585542</v>
       </c>
       <c r="R8" t="n">
-        <v>6577547</v>
+        <v>6577578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118887077</v>
+        <v>118887003</v>
       </c>
       <c r="B9" t="n">
-        <v>105502</v>
+        <v>100024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1547,20 +1547,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1571,14 +1571,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Piltorp (Piltorp), Srm</t>
+          <t>Skogstorp (Skogstorp), Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585542</v>
+        <v>585527</v>
       </c>
       <c r="R9" t="n">
-        <v>6577578</v>
+        <v>6577547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
